--- a/stories/arbres/ATOM-TMP.SEM.001-06.xlsx
+++ b/stories/arbres/ATOM-TMP.SEM.001-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>François s'assoit sur le tapis du salon. Maman a une chaîne de sept perles. Chaque perle est un jour. Maman dit : il y a sept jours. François touche une perle. C'est lisse. Maman dit : lundi, on met les chaussures. Mardi, on prend le cartable. Mercredi, on reste un peu à la maison. Jeudi, on revoit les copains. Vendredi, on chante à l'école. Samedi, on va au marché. Dimanche, on mange des crêpes. Maman dit : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. François répète les sept jours dans l'ordre. Parce qu'il les dit dans l'ordre, il se souvient. Maman avance une perle. François dit : après lundi, c'est mardi. Maman sourit. Ils recommencent une fois. Sept jours. Toujours dans l'ordre. François pose la perle sur mercredi. Maman dit : encore. François dit toute la liste. Lundi commence. Dimanche termine.</t>
+          <t>François s'assoit sur le tapis du salon. Maman a une chaîne de sept perles. Chaque perle est un jour. Il y a sept jours. François touche une perle. C'est lisse. Lundi, on met les chaussures. Mardi, on prend le cartable. Mercredi, on reste un peu à la maison. Jeudi, on revoit les copains. Vendredi, on chante à l'école. Samedi, on va au marché. Dimanche, on mange des crêpes. Lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. François répète les sept jours dans l'ordre. Parce qu'il les dit dans l'ordre, il se souvient. Maman avance une perle. Après lundi, c'est mardi. Maman sourit. Ils recommencent une fois. Sept jours. Toujours dans l'ordre. François pose la perle sur mercredi. Encore. François dit toute la liste. Lundi commence. Dimanche termine.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,20 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|François s'assoit sur le tapis du salon. Maman a une chaîne de sept perles. Chaque perle est un jour.
+maman|Il y a sept jours.
+narrateur|François touche une perle. C'est lisse.
+maman|Lundi, on met les chaussures. Mardi, on prend le cartable. Mercredi, on reste un peu à la maison. Jeudi, on revoit les copains. Vendredi, on chante à l'école. Samedi, on va au marché. Dimanche, on mange des crêpes.
+maman|Lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche.
+narrateur|François répète les sept jours dans l'ordre. Parce qu'il les dit dans l'ordre, il se souvient. Maman avance une perle.
+enfant-m|Après lundi, c'est mardi. Maman sourit. Ils recommencent une fois. Sept jours. Toujours dans l'ordre.
+narrateur|François pose la perle sur mercredi.
+maman|Encore.
+narrateur|François dit toute la liste. Lundi commence. Dimanche termine.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1495,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Après lundi, quel jour vient ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1668,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|François a dit les sept jours dans l'ordre. Lundi commence. Dimanche termine.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1831,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|François pose la perle sur lundi. Maman range la chaîne.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1998,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2038,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-TMP.SEM.001-06.xlsx
+++ b/stories/arbres/ATOM-TMP.SEM.001-06.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1319,6 +1324,11 @@
 narrateur|François dit toute la liste. Lundi commence. Dimanche termine.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1502,6 +1512,7 @@
           <t>narrateur|Après lundi, quel jour vient ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1673,6 +1684,7 @@
           <t>narrateur|François a dit les sept jours dans l'ordre. Lundi commence. Dimanche termine.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1836,6 +1848,7 @@
           <t>narrateur|François pose la perle sur lundi. Maman range la chaîne.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2003,6 +2016,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2021,7 +2035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2045,6 +2059,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2059,7 +2087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2246,6 +2274,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-TMP.SEM.001-06.xlsx
+++ b/stories/arbres/ATOM-TMP.SEM.001-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>François dit les sept jours</t>
+          <t>La flaque de mardi</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Chouchou veut la grande flaque de la cour. Lundi, les chaussettes rouges sèchent, encore mouillées. Mardi, une chaussette reste humide. Elle attend un peu. Puis la flaque.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>François s'assoit sur le tapis du salon. Maman a une chaîne de sept perles. Chaque perle est un jour. Il y a sept jours. François touche une perle. C'est lisse. Lundi, on met les chaussures. Mardi, on prend le cartable. Mercredi, on reste un peu à la maison. Jeudi, on revoit les copains. Vendredi, on chante à l'école. Samedi, on va au marché. Dimanche, on mange des crêpes. Lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. François répète les sept jours dans l'ordre. Parce qu'il les dit dans l'ordre, il se souvient. Maman avance une perle. Après lundi, c'est mardi. Maman sourit. Ils recommencent une fois. Sept jours. Toujours dans l'ordre. François pose la perle sur mercredi. Encore. François dit toute la liste. Lundi commence. Dimanche termine.</t>
+          <t>Les chaussettes rouges dansent sur la corde. Une goutte tombe du talon. Elle fait un rond sur le carrelage. Le radiateur tic tout doux. Tu as vu la goutte, Chouchou ? Elle tombe encore. C'est lundi. Lundi, les chaussettes sèchent. En ce moment, Chouchou touche une chaussette. Elle est froide, encore lourde d'eau. Je veux la flaque. La grande, dans la cour. Tes chaussettes sont mouillées. Demain, c'est mardi. Mardi, elles seront sèches. On y va maintenant ? Les pieds seraient froids. Chouchou appuie le nez à la vitre. La flaque de la cour brille, ronde. La pluie a cessé. Elle m'attend. Elle attend mardi aussi. La semaine a sept jours. Quel jour vient après lundi ? Mardi. Oui. Une autre goutte tombe. Le rond sur le carrelage s'agrandit. Je peux les aider à sécher ? On les rapproche du radiateur. Chouchou tend la corde un peu. Les chaussettes rouges dansent plus près. Merci, Chouchou. Le tic du radiateur continue. La corde tremble encore un peu. Demain, je saute. Mardi, oui.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;François s'assoit sur le tapis du salon. Maman a une chaîne de &lt;emphasis level="moderate"&gt;sept&lt;/emphasis&gt; perles. Chaque perle est un jour. Maman dit : il y a sept jours. François touche une perle. C'est lisse. Maman dit : lundi, on met les chaussures. Mardi, on prend le cartable. Mercredi, on reste un peu à la maison. Jeudi, on revoit les copains. Vendredi, on chante à l'école. Samedi, on va au marché. Dimanche, on mange des crêpes. Maman dit : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. François répète les sept jours dans l'ordre. Parce qu'il les dit dans l'ordre, il se souvient. Maman avance une perle. François dit : après lundi, c'est mardi. Maman sourit. Ils recommencent une fois. Sept jours. Toujours dans l'ordre. François pose la perle sur mercredi. Maman dit : encore. François dit toute la liste. Lundi commence. Dimanche termine.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Les chaussettes rouges dansent sur la corde. Une goutte tombe du talon. Elle fait un rond sur le carrelage. Le radiateur tic tout doux. Tu as vu la goutte, Chouchou ? Elle tombe encore. C'est lundi. Lundi, les chaussettes sèchent. En ce moment, Chouchou touche une chaussette. Elle est froide, encore lourde d'eau. Je veux la flaque. La grande, dans la cour. Tes chaussettes sont mouillées. Demain, c'est mardi. Mardi, elles seront sèches. On y va maintenant ? Les pieds seraient froids. Chouchou appuie le nez à la vitre. La flaque de la cour brille, ronde. La pluie a cessé. Elle m'attend. Elle attend mardi aussi. La semaine a sept jours. Quel jour vient après lundi ? Mardi. Oui. Une autre goutte tombe. Le rond sur le carrelage s'agrandit. Je peux les aider à sécher ? On les rapproche du radiateur. Chouchou tend la corde un peu. Les chaussettes rouges dansent plus près. Merci, Chouchou. Le tic du radiateur continue. La corde tremble encore un peu. Demain, je saute. Mardi, oui.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1240,7 +1252,7 @@
         <v>0.92</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,16 +1324,43 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|François s'assoit sur le tapis du salon. Maman a une chaîne de sept perles. Chaque perle est un jour.
-maman|Il y a sept jours.
-narrateur|François touche une perle. C'est lisse.
-maman|Lundi, on met les chaussures. Mardi, on prend le cartable. Mercredi, on reste un peu à la maison. Jeudi, on revoit les copains. Vendredi, on chante à l'école. Samedi, on va au marché. Dimanche, on mange des crêpes.
-maman|Lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche.
-narrateur|François répète les sept jours dans l'ordre. Parce qu'il les dit dans l'ordre, il se souvient. Maman avance une perle.
-enfant-m|Après lundi, c'est mardi. Maman sourit. Ils recommencent une fois. Sept jours. Toujours dans l'ordre.
-narrateur|François pose la perle sur mercredi.
-maman|Encore.
-narrateur|François dit toute la liste. Lundi commence. Dimanche termine.</t>
+          <t>narrateur|Les chaussettes rouges dansent sur la corde.
+narrateur|Une goutte tombe du talon.
+narrateur|Elle fait un rond sur le carrelage.
+narrateur|Le radiateur tic tout doux.
+maman|Tu as vu la goutte, Chouchou ?
+enfant-f|Elle tombe encore.
+maman|C'est lundi.
+maman|Lundi, les chaussettes sèchent.
+narrateur|En ce moment, Chouchou touche une chaussette.
+narrateur|Elle est froide, encore lourde d'eau.
+enfant-f|Je veux la flaque.
+enfant-f|La grande, dans la cour.
+maman|Tes chaussettes sont mouillées.
+maman|Demain, c'est mardi.
+maman|Mardi, elles seront sèches.
+enfant-f|On y va maintenant ?
+maman|Les pieds seraient froids.
+narrateur|Chouchou appuie le nez à la vitre.
+narrateur|La flaque de la cour brille, ronde.
+narrateur|La pluie a cessé.
+enfant-f|Elle m'attend.
+maman|Elle attend mardi aussi.
+maman|La semaine a sept jours.
+maman|Quel jour vient après lundi ?
+enfant-f|Mardi.
+maman|Oui.
+narrateur|Une autre goutte tombe.
+narrateur|Le rond sur le carrelage s'agrandit.
+enfant-f|Je peux les aider à sécher ?
+maman|On les rapproche du radiateur.
+narrateur|Chouchou tend la corde un peu.
+narrateur|Les chaussettes rouges dansent plus près.
+maman|Merci, Chouchou.
+narrateur|Le tic du radiateur continue.
+narrateur|La corde tremble encore un peu.
+enfant-f|Demain, je saute.
+maman|Mardi, oui.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1358,7 +1397,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Après lundi, quel jour vient ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Après lundi, quel jour vient ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1373,7 +1412,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>mardi | c'est mardi | le mardi</t>
+          <t>mardi | le mardi | c'est mardi</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1388,7 +1427,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Lundi, puis mardi. Quel jour après lundi ?</t>
+          <t>Lundi, les chaussettes sèchent. Quel jour vient après ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1437,7 +1476,7 @@
         <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1512,7 +1551,6 @@
           <t>narrateur|Après lundi, quel jour vient ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1537,12 +1575,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>François a dit les sept jours dans l'ordre. Lundi commence. Dimanche termine.</t>
+          <t>Le lendemain, le carrelage est sec. Une chaussette est légère. L'autre reste un peu froide. C'est mardi, Chouchou. Celle-là est encore humide. On la pose un moment ici. Chouchou pose la chaussette sur le radiateur. Le tissu fume un tout petit peu. Elle sèche. Puis les bottes. Les bottes jaunes attendent sous le banc. Chouchou enfile la sèche d'abord. Puis l'autre, enfin tiède. Je suis prête. La flaque est encore là. Tu as attendu mardi. La poignée de la porte est froide.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;François a dit les &lt;emphasis level="moderate"&gt;sept&lt;/emphasis&gt; jours dans l'ordre. Lundi commence. Dimanche termine.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le lendemain, le carrelage est sec. Une chaussette est légère. L'autre reste un peu froide. C'est mardi, Chouchou. Celle-là est encore humide. On la pose un moment ici. Chouchou pose la chaussette sur le radiateur. Le tissu fume un tout petit peu. Elle sèche. Puis les bottes. Les bottes jaunes attendent sous le banc. Chouchou enfile la sèche d'abord. Puis l'autre, enfin tiède. Je suis prête. La flaque est encore là. Tu as attendu mardi. La poignée de la porte est froide.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1605,7 +1643,7 @@
         <v>0.92</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1681,10 +1719,25 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|François a dit les sept jours dans l'ordre. Lundi commence. Dimanche termine.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Le lendemain, le carrelage est sec.
+narrateur|Une chaussette est légère.
+narrateur|L'autre reste un peu froide.
+maman|C'est mardi, Chouchou.
+enfant-f|Celle-là est encore humide.
+maman|On la pose un moment ici.
+narrateur|Chouchou pose la chaussette sur le radiateur.
+narrateur|Le tissu fume un tout petit peu.
+enfant-f|Elle sèche.
+maman|Puis les bottes.
+narrateur|Les bottes jaunes attendent sous le banc.
+narrateur|Chouchou enfile la sèche d'abord.
+narrateur|Puis l'autre, enfin tiède.
+enfant-f|Je suis prête.
+maman|La flaque est encore là.
+maman|Tu as attendu mardi.
+narrateur|La poignée de la porte est froide.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1709,12 +1762,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>François pose la perle sur lundi. Maman range la chaîne.</t>
+          <t>La cour brille encore. La flaque est ronde, un peu brune. Lundi, les chaussettes. Mardi, la flaque. J'y vais. Chouchou pose un pied. L'eau fait plouf, tout doux. Elle est froide ! Les bottes tiennent. Elle pose l'autre pied. Deux ronds s'ouvrent dans l'eau. Je suis au milieu. Oui. Tes chaussettes sont sèches, dedans. Une feuille tourne à la surface. Chouchou la pousse du bout de la botte. Encore un plouf. Encore un, tout doux. Les bottes jaunes ont des gouttes. La cour sent la terre mouillée.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;François pose la perle sur lundi. Maman range la chaîne.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>La cour brille encore. La flaque est ronde, un peu brune. Lundi, les chaussettes. Mardi, la flaque. J'y vais. Chouchou pose un pied. L'eau fait plouf, tout doux. Elle est froide ! Les bottes tiennent. Elle pose l'autre pied. Deux ronds s'ouvrent dans l'eau. Je suis au milieu. Oui. Tes chaussettes sont sèches, dedans. Une feuille tourne à la surface. Chouchou la pousse du bout de la botte. Encore un plouf. Encore un, tout doux. Les bottes jaunes ont des gouttes. La cour sent la terre mouillée.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1777,7 +1830,7 @@
         <v>0.92</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1845,10 +1898,28 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|François pose la perle sur lundi. Maman range la chaîne.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|La cour brille encore.
+narrateur|La flaque est ronde, un peu brune.
+maman|Lundi, les chaussettes.
+maman|Mardi, la flaque.
+enfant-f|J'y vais.
+narrateur|Chouchou pose un pied.
+narrateur|L'eau fait plouf, tout doux.
+enfant-f|Elle est froide !
+maman|Les bottes tiennent.
+narrateur|Elle pose l'autre pied.
+narrateur|Deux ronds s'ouvrent dans l'eau.
+enfant-f|Je suis au milieu.
+maman|Oui.
+maman|Tes chaussettes sont sèches, dedans.
+narrateur|Une feuille tourne à la surface.
+narrateur|Chouchou la pousse du bout de la botte.
+enfant-f|Encore un plouf.
+maman|Encore un, tout doux.
+narrateur|Les bottes jaunes ont des gouttes.
+narrateur|La cour sent la terre mouillée.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1873,12 +1944,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Les bottes jaunes sèchent près de la porte. J'ai eu ma flaque. Oui. Lundi la corde, mardi l'eau. Les chaussettes rouges pendent, enfin légères.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Les bottes jaunes sèchent près de la porte. J'ai eu ma flaque. Oui. Lundi la corde, mardi l'eau. Les chaussettes rouges pendent, enfin légères.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1934,14 +2005,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2013,10 +2084,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Les bottes jaunes sèchent près de la porte.
+enfant-f|J'ai eu ma flaque.
+maman|Oui.
+maman|Lundi la corde, mardi l'eau.
+narrateur|Les chaussettes rouges pendent, enfin légères.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2035,7 +2109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2073,6 +2147,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-TMP.SEM.001-06.xlsx
+++ b/stories/arbres/ATOM-TMP.SEM.001-06.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>salon</t>
+          <t>entrée le lundi, cour le mardi</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>François, maman</t>
+          <t>Chouchou, maman</t>
         </is>
       </c>
     </row>
